--- a/data/samples/relatorio_sistema_exemplo.xlsx
+++ b/data/samples/relatorio_sistema_exemplo.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conciliação" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relatorio" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,134 +426,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Emissão:13/05/2026 19:12:54</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Total de registros:16</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Usuário: EXEMPLO</t>
+          <t>Emissão: 05/05/2026 · Total: 10 registros · Usuário: TESTE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tipo de Movimento</t>
+          <t>Dt. Lançamento</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Histórico</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Núm. Documento</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Vlr. Lançamento</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Receita/Despesa</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Conta Bancária</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Conciliado</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Vlr. Lançamento</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Receita/Despesa</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Dt. Lançamento</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Histórico</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Núm. Único Bancário</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Usuário</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Conta Bancária</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PIX RECEBIDO CLIENTE A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Despesa</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>Bradesco-CC-12345</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FORNECEDOR ALPHA LTDA</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>800000</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PIX ENVIADO FORNECEDOR X</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -562,44 +520,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>Bradesco-CC-12345</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BETA INDUSTRIA SA</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>800001</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>102</v>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BOLETO PAGAMENTO LUZ</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>BOL-123</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3000</v>
+        <v>350</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -608,44 +555,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>Bradesco-CC-12345</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>GAMMA COMERCIO ME</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>800002</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>103</v>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TAR LIQ COB</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4000</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -654,44 +590,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>Bradesco-CC-12345</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DELTA SERVICOS LTDA</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>800003</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>104</v>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TAR LIQ COB</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5000</v>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -700,90 +625,64 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>Bradesco-CC-12345</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EPSILON DISTRIB SA</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>800004</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TED RECEBIDA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>5000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Despesa</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>Bradesco-CC-12345</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TAR LIQ COB COM REG COMPE</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>900001</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DARF FEDERAL</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>DARF1</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1200</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -792,136 +691,95 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>Bradesco-CC-12345</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TAR LIQ COB CORBAN DIGITAL</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>900001</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>200</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INDEVIDA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>250</v>
+        <v>999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Despesa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>Bradesco-CC-12345</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CLIENTE NORTE LTDA</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>700000</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>201</v>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BOLETO ALUGUEL</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>B-99</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>350</v>
+        <v>2500</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Despesa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>Itau-CC-67890</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CLIENTE SUL ME</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>700001</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>202</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RECEBIMENTO CLIENTE B</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>450</v>
+        <v>3200</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -930,301 +788,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>Itau-CC-67890</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CLIENTE LESTE SA</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>700002</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>203</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>550</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Receita</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>CLIENTE OESTE LTDA</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>700003</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Transferência</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Despesa</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>APLICACAO CONTAMAX</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>950001</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>301</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Despesa</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>FORNECEDOR ALPHA LTDA</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>950002</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>310506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>800.5</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Despesa</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PAGAMENTO DE TITULO</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>950003</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>999</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>555.55</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Despesa</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LANCAMENTO INDEVIDO TESTE</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Financeiro</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>105</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1050</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Despesa</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>FORNECEDOR ALPHA LTDA (divergente)</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>999001</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>DEBORA.SILVA</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>BCO-EXEMPLO-001</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
